--- a/data/trans_dic/P62A$viudedad-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P62A$viudedad-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de viudedad</t>
+          <t>Población que, al menos, percibe una pensión de viudedad (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 31,08</t>
+          <t>4,24; 30,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,68; 70,34</t>
+          <t>37,96; 70,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,61; 39,42</t>
+          <t>16,01; 39,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 32,68</t>
+          <t>10,26; 33,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 13,07</t>
+          <t>1,49; 13,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 31,68</t>
+          <t>14,03; 31,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,08; 20,34</t>
+          <t>8,22; 19,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 16,84</t>
+          <t>5,18; 16,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 18,15</t>
+          <t>4,04; 17,7</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,11</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,89; 25,75</t>
+          <t>11,96; 25,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,09; 67,91</t>
+          <t>45,92; 68,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,8; 63,68</t>
+          <t>40,61; 63,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,33; 68,53</t>
+          <t>47,1; 69,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,07</t>
+          <t>5,66; 14,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,1; 29,08</t>
+          <t>16,59; 29,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,47; 27,45</t>
+          <t>15,85; 28,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,39; 28,5</t>
+          <t>17,2; 28,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 18,11</t>
+          <t>10,2; 18,88</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,15</t>
+          <t>0,0; 12,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>0,0; 5,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,93; 41,05</t>
+          <t>25,75; 40,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,82; 67,76</t>
+          <t>43,12; 66,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,12; 66,21</t>
+          <t>42,0; 65,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,18; 37,27</t>
+          <t>16,51; 37,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 15,53</t>
+          <t>5,81; 15,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 33,81</t>
+          <t>19,12; 33,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,78; 34,88</t>
+          <t>20,19; 34,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 19,54</t>
+          <t>8,21; 19,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,18; 26,62</t>
+          <t>16,98; 26,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 7,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,06; 55,97</t>
+          <t>32,18; 56,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,91; 49,58</t>
+          <t>30,47; 50,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,75; 54,84</t>
+          <t>30,0; 53,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 10,32</t>
+          <t>2,32; 9,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,75; 28,96</t>
+          <t>14,41; 28,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,45; 26,02</t>
+          <t>14,1; 25,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,17; 25,93</t>
+          <t>12,62; 25,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,68</t>
+          <t>1,72; 6,33</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 21,65</t>
+          <t>4,79; 21,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,8; 59,91</t>
+          <t>23,3; 57,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,59; 49,77</t>
+          <t>21,77; 49,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 33,12</t>
+          <t>10,07; 30,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 16,58</t>
+          <t>5,38; 16,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,91; 27,32</t>
+          <t>10,05; 26,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 25,48</t>
+          <t>10,48; 26,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 15,65</t>
+          <t>4,59; 15,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 16,27</t>
+          <t>6,62; 15,8</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>0,0; 8,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,32; 32,36</t>
+          <t>17,51; 32,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,53; 72,73</t>
+          <t>43,29; 71,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,02; 71,25</t>
+          <t>44,54; 70,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,19; 73,74</t>
+          <t>42,5; 74,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 20,08</t>
+          <t>8,46; 20,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,89; 36,25</t>
+          <t>17,1; 34,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 34,08</t>
+          <t>18,86; 33,65</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,94; 31,55</t>
+          <t>14,86; 30,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,33; 24,79</t>
+          <t>15,02; 25,42</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,8; 18,84</t>
+          <t>8,76; 18,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,42; 58,51</t>
+          <t>40,58; 58,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,8; 52,72</t>
+          <t>35,32; 52,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,08; 44,14</t>
+          <t>27,68; 43,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 11,4</t>
+          <t>1,06; 11,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,53; 27,58</t>
+          <t>17,66; 28,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,8; 26,62</t>
+          <t>16,96; 27,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,5; 23,26</t>
+          <t>13,59; 23,04</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,91</t>
+          <t>2,5; 12,81</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,4; 17,91</t>
+          <t>9,39; 17,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,06; 49,94</t>
+          <t>31,95; 48,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,24; 46,26</t>
+          <t>30,1; 46,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,37; 38,63</t>
+          <t>23,61; 38,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 8,08</t>
+          <t>3,05; 8,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,98; 23,12</t>
+          <t>13,86; 23,15</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,27; 21,3</t>
+          <t>13,01; 21,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,33; 17,87</t>
+          <t>10,72; 18,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 12,23</t>
+          <t>7,12; 12,54</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,98; 18,76</t>
+          <t>13,88; 18,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44,97; 53,3</t>
+          <t>45,58; 53,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,81; 47,18</t>
+          <t>39,27; 46,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,94; 39,75</t>
+          <t>31,9; 39,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,94</t>
+          <t>3,18; 8,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,62; 24,17</t>
+          <t>19,55; 23,93</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18,24; 22,3</t>
+          <t>18,26; 22,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14,29; 18,06</t>
+          <t>14,41; 18,22</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,22; 12,97</t>
+          <t>7,07; 12,91</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de viudedad</t>
+          <t>Población que, al menos, percibe una pensión de viudedad (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1742</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2052</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1889</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1118; 7535</t>
+          <t>1028; 7368</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13738; 24984</t>
+          <t>13483; 24965</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12115; 27125</t>
+          <t>11018; 26852</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5824; 17967</t>
+          <t>5639; 18576</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>496; 4070</t>
+          <t>463; 4226</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12685; 27978</t>
+          <t>12392; 28221</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11704; 29470</t>
+          <t>11915; 28854</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5518; 19064</t>
+          <t>5868; 19008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2499; 10054</t>
+          <t>2236; 9806</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1965</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5442</t>
+          <t>0; 5655</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1938</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16036; 34716</t>
+          <t>16121; 34563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35711; 53786</t>
+          <t>36371; 53930</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37153; 56601</t>
+          <t>36099; 56549</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43369; 62792</t>
+          <t>43158; 63414</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6990; 18391</t>
+          <t>6912; 17512</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34214; 58203</t>
+          <t>33198; 58498</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34217; 60723</t>
+          <t>35073; 62150</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39379; 68448</t>
+          <t>41306; 68163</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26015; 46512</t>
+          <t>26212; 48484</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1835</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 13282</t>
+          <t>0; 10022</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5538</t>
+          <t>0; 4810</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23795; 37675</t>
+          <t>23634; 37625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29123; 45039</t>
+          <t>28662; 44442</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31826; 50026</t>
+          <t>31733; 49322</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12928; 29776</t>
+          <t>13193; 29749</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5254; 13007</t>
+          <t>4865; 12921</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26595; 47732</t>
+          <t>26992; 47779</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31207; 55035</t>
+          <t>31863; 54353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13277; 33186</t>
+          <t>13948; 32559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30151; 46726</t>
+          <t>29796; 46970</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1764</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2087</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1832</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4443</t>
+          <t>0; 5654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20786; 36291</t>
+          <t>20866; 36645</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31123; 49927</t>
+          <t>30680; 50897</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23037; 42458</t>
+          <t>23230; 41092</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1993; 8326</t>
+          <t>1872; 7751</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19882; 39053</t>
+          <t>19423; 38550</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29346; 52838</t>
+          <t>28633; 52320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22915; 45121</t>
+          <t>21950; 44329</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2500; 10673</t>
+          <t>2749; 10116</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1731</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2076</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1799</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1426; 6798</t>
+          <t>1504; 6830</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8316; 20936</t>
+          <t>8141; 20249</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10621; 23403</t>
+          <t>10234; 23322</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5684; 18941</t>
+          <t>5759; 17405</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2269; 6907</t>
+          <t>2240; 7002</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7946; 21918</t>
+          <t>8064; 20941</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10222; 24709</t>
+          <t>10163; 25656</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5667; 19389</t>
+          <t>5686; 19616</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4794; 11883</t>
+          <t>4833; 11540</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5269</t>
+          <t>0; 5676</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1977</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1816</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13845; 25866</t>
+          <t>13993; 26191</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20213; 34567</t>
+          <t>20575; 34015</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27661; 42827</t>
+          <t>26770; 42623</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18686; 32663</t>
+          <t>18826; 33025</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4616; 12037</t>
+          <t>5071; 12335</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20917; 40145</t>
+          <t>18940; 38515</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24829; 45817</t>
+          <t>25357; 45229</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17668; 37305</t>
+          <t>17569; 36251</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21443; 34679</t>
+          <t>21004; 35557</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1864</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2119</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2047</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13971; 29894</t>
+          <t>13894; 30065</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>48066; 69582</t>
+          <t>48265; 69816</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53755; 79159</t>
+          <t>53032; 79188</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41348; 67400</t>
+          <t>42269; 67003</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3146; 39196</t>
+          <t>3658; 40301</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>45896; 72183</t>
+          <t>46233; 73549</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51949; 82329</t>
+          <t>52454; 83519</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41348; 71261</t>
+          <t>41644; 70596</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10954; 64883</t>
+          <t>12541; 64372</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 5004</t>
+          <t>0; 6327</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2171</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18945; 36112</t>
+          <t>18931; 36062</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>41241; 64245</t>
+          <t>41110; 62868</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46831; 71631</t>
+          <t>46616; 72419</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41819; 69125</t>
+          <t>42236; 68948</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5335; 14095</t>
+          <t>5319; 14420</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41491; 68629</t>
+          <t>41135; 68703</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>46371; 74450</t>
+          <t>45490; 75536</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>40554; 70132</t>
+          <t>42091; 72492</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>27113; 46016</t>
+          <t>26783; 47178</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 6720</t>
+          <t>0; 6964</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 12367</t>
+          <t>0; 11249</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 5579</t>
+          <t>0; 5233</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112018; 150339</t>
+          <t>111262; 149374</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>259080; 307049</t>
+          <t>262575; 309304</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>297014; 352025</t>
+          <t>292984; 349248</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>235428; 293005</t>
+          <t>235152; 292433</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>29687; 83784</t>
+          <t>29778; 83927</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>257740; 317638</t>
+          <t>256818; 314441</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>294999; 360593</t>
+          <t>295256; 361475</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>234046; 295889</t>
+          <t>236126; 298549</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>125638; 225476</t>
+          <t>122995; 224531</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$viudedad-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P62A$viudedad-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 30,39</t>
+          <t>6,03; 30,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,96; 70,29</t>
+          <t>37,2; 70,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,01; 39,02</t>
+          <t>17,46; 38,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 33,79</t>
+          <t>10,01; 33,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,57</t>
+          <t>1,53; 14,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,03; 31,96</t>
+          <t>13,98; 32,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 19,91</t>
+          <t>8,12; 20,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 16,79</t>
+          <t>4,72; 16,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 17,7</t>
+          <t>4,42; 17,22</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,96; 25,64</t>
+          <t>11,55; 25,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,92; 68,09</t>
+          <t>46,34; 69,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,61; 63,62</t>
+          <t>41,5; 63,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,1; 69,2</t>
+          <t>47,65; 69,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 14,35</t>
+          <t>5,38; 13,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,59; 29,23</t>
+          <t>17,22; 28,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,85; 28,09</t>
+          <t>16,04; 27,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,2; 28,38</t>
+          <t>17,1; 28,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 18,88</t>
+          <t>10,0; 18,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,19</t>
+          <t>0,0; 12,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 7,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,75; 40,99</t>
+          <t>25,55; 41,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,12; 66,87</t>
+          <t>43,94; 67,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,0; 65,27</t>
+          <t>40,83; 65,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,51; 37,24</t>
+          <t>16,12; 36,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 15,43</t>
+          <t>5,82; 14,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,12; 33,84</t>
+          <t>19,32; 34,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,19; 34,44</t>
+          <t>20,23; 35,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 19,17</t>
+          <t>7,88; 19,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,98; 26,76</t>
+          <t>16,89; 26,43</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,18; 56,51</t>
+          <t>31,25; 55,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,47; 50,54</t>
+          <t>29,61; 49,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,0; 53,07</t>
+          <t>30,25; 54,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,61</t>
+          <t>2,55; 10,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,41; 28,59</t>
+          <t>14,49; 28,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 25,76</t>
+          <t>14,53; 25,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,62; 25,48</t>
+          <t>12,55; 26,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,33</t>
+          <t>1,46; 5,87</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 21,76</t>
+          <t>5,56; 23,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,3; 57,94</t>
+          <t>23,45; 57,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,77; 49,6</t>
+          <t>22,4; 50,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,07; 30,43</t>
+          <t>10,01; 32,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 16,81</t>
+          <t>5,39; 16,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,05; 26,11</t>
+          <t>10,13; 27,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 26,46</t>
+          <t>10,54; 25,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 15,83</t>
+          <t>4,37; 15,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 15,8</t>
+          <t>6,64; 16,63</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,98</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,51; 32,77</t>
+          <t>17,65; 31,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,29; 71,57</t>
+          <t>43,65; 73,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,54; 70,91</t>
+          <t>45,96; 69,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,5; 74,56</t>
+          <t>43,01; 74,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,46; 20,58</t>
+          <t>7,82; 19,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,1; 34,78</t>
+          <t>19,26; 35,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,86; 33,65</t>
+          <t>18,21; 33,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,86; 30,66</t>
+          <t>14,79; 32,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,02; 25,42</t>
+          <t>15,04; 25,15</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,76; 18,95</t>
+          <t>7,94; 17,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,58; 58,71</t>
+          <t>40,16; 58,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,32; 52,74</t>
+          <t>36,52; 53,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,68; 43,88</t>
+          <t>28,56; 45,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 11,72</t>
+          <t>6,51; 14,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,66; 28,1</t>
+          <t>17,67; 28,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,96; 27,01</t>
+          <t>16,99; 26,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,59; 23,04</t>
+          <t>13,29; 22,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 12,81</t>
+          <t>8,55; 14,35</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1712,47 +1712,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,39; 17,89</t>
+          <t>9,72; 17,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,95; 48,87</t>
+          <t>31,3; 49,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,1; 46,77</t>
+          <t>30,59; 47,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,61; 38,53</t>
+          <t>23,93; 38,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,26</t>
+          <t>3,45; 8,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,86; 23,15</t>
+          <t>13,64; 23,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,01; 21,61</t>
+          <t>12,96; 21,38</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,72; 18,47</t>
+          <t>10,84; 18,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,12; 12,54</t>
+          <t>7,36; 12,68</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1842,57 +1842,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,88; 18,64</t>
+          <t>13,36; 18,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,58; 53,69</t>
+          <t>45,35; 53,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,27; 46,81</t>
+          <t>39,83; 47,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,9; 39,68</t>
+          <t>32,11; 39,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,95</t>
+          <t>6,87; 9,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,55; 23,93</t>
+          <t>19,41; 23,81</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18,26; 22,35</t>
+          <t>18,14; 22,27</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14,41; 18,22</t>
+          <t>14,3; 18,16</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,07; 12,91</t>
+          <t>10,8; 13,58</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5799</t>
         </is>
       </c>
     </row>
@@ -2224,47 +2224,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1028; 7368</t>
+          <t>1525; 7785</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13483; 24965</t>
+          <t>13213; 25216</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11018; 26852</t>
+          <t>12016; 26798</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5639; 18576</t>
+          <t>5502; 18437</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>463; 4226</t>
+          <t>480; 4580</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12392; 28221</t>
+          <t>12344; 28967</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11915; 28854</t>
+          <t>11770; 29062</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5868; 19008</t>
+          <t>5348; 19228</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2236; 9806</t>
+          <t>2503; 9762</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23961</t>
+          <t>25268</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35222</t>
+          <t>36527</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5655</t>
+          <t>0; 5389</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2432,47 +2432,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16121; 34563</t>
+          <t>16527; 36098</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36371; 53930</t>
+          <t>36708; 54756</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36099; 56549</t>
+          <t>36892; 56158</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43158; 63414</t>
+          <t>43664; 63487</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6912; 17512</t>
+          <t>6827; 17612</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33198; 58498</t>
+          <t>34460; 57623</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35073; 62150</t>
+          <t>35494; 61588</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41306; 68163</t>
+          <t>41066; 68954</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26212; 48484</t>
+          <t>27016; 48818</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>29549</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>37798</t>
         </is>
       </c>
     </row>
@@ -2630,57 +2630,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 10022</t>
+          <t>0; 9958</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4810</t>
+          <t>0; 6624</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23634; 37625</t>
+          <t>23022; 37505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28662; 44442</t>
+          <t>29207; 44954</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31733; 49322</t>
+          <t>30853; 49799</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13193; 29749</t>
+          <t>12883; 29130</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4865; 12921</t>
+          <t>5009; 12682</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26992; 47779</t>
+          <t>27284; 49007</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31863; 54353</t>
+          <t>31926; 55385</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13948; 32559</t>
+          <t>13376; 32302</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29796; 46970</t>
+          <t>29755; 46568</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5651</t>
         </is>
       </c>
     </row>
@@ -2848,47 +2848,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5654</t>
+          <t>0; 4462</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20866; 36645</t>
+          <t>20262; 36118</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30680; 50897</t>
+          <t>29815; 49873</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23230; 41092</t>
+          <t>23418; 42213</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1872; 7751</t>
+          <t>2195; 8822</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19423; 38550</t>
+          <t>19538; 37832</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28633; 52320</t>
+          <t>29509; 51554</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21950; 44329</t>
+          <t>21831; 46061</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2749; 10116</t>
+          <t>2559; 10270</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>8545</t>
         </is>
       </c>
     </row>
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1504; 6830</t>
+          <t>1859; 7917</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8141; 20249</t>
+          <t>8195; 19921</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10234; 23322</t>
+          <t>10534; 23855</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5759; 17405</t>
+          <t>5728; 18862</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2240; 7002</t>
+          <t>2333; 7106</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8064; 20941</t>
+          <t>8126; 21887</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10163; 25656</t>
+          <t>10218; 25001</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5686; 19616</t>
+          <t>5421; 19419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4833; 11540</t>
+          <t>5091; 12762</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19359</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>27058</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5676</t>
+          <t>0; 5295</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3264,47 +3264,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13993; 26191</t>
+          <t>13958; 24965</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20575; 34015</t>
+          <t>20745; 34940</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26770; 42623</t>
+          <t>27625; 41832</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18826; 33025</t>
+          <t>19051; 33135</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5071; 12335</t>
+          <t>4794; 12175</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18940; 38515</t>
+          <t>21326; 39656</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25357; 45229</t>
+          <t>24476; 45290</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17569; 36251</t>
+          <t>17485; 37923</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21004; 35557</t>
+          <t>21111; 35302</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>22978</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14221</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35482</t>
+          <t>39391</t>
         </is>
       </c>
     </row>
@@ -3472,47 +3472,47 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13894; 30065</t>
+          <t>15121; 33222</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>48265; 69816</t>
+          <t>47755; 69647</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53032; 79188</t>
+          <t>54829; 80108</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42269; 67003</t>
+          <t>43618; 68795</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3658; 40301</t>
+          <t>10981; 24255</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46233; 73549</t>
+          <t>46248; 73854</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52454; 83519</t>
+          <t>52545; 83010</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41644; 70596</t>
+          <t>40707; 68231</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12541; 64372</t>
+          <t>30698; 51515</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26497</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>40771</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6327</t>
+          <t>0; 3974</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3680,47 +3680,47 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18931; 36062</t>
+          <t>21793; 40277</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>41110; 62868</t>
+          <t>40269; 63979</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46616; 72419</t>
+          <t>47371; 72893</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>42236; 68948</t>
+          <t>42814; 68480</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5319; 14420</t>
+          <t>6910; 17464</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41135; 68703</t>
+          <t>40495; 69169</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45490; 75536</t>
+          <t>45298; 74719</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42091; 72492</t>
+          <t>42539; 72359</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>26783; 47178</t>
+          <t>31230; 53805</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>135375</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>190581</t>
+          <t>201539</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 6964</t>
+          <t>0; 6903</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 11249</t>
+          <t>0; 11048</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 5233</t>
+          <t>0; 5593</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111262; 149374</t>
+          <t>116805; 157654</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>262575; 309304</t>
+          <t>261261; 309755</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>292984; 349248</t>
+          <t>297201; 351962</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>235152; 292433</t>
+          <t>236685; 291509</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>29778; 83927</t>
+          <t>55192; 78578</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>256818; 314441</t>
+          <t>255092; 312903</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>295256; 361475</t>
+          <t>293362; 360159</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>236126; 298549</t>
+          <t>234246; 297540</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>122995; 224531</t>
+          <t>181275; 227978</t>
         </is>
       </c>
     </row>
